--- a/multiSchoolOutput/02_Centre_for_Open_Learning/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/02_Centre_for_Open_Learning/solution_weeks_9_10.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0001_02_2.351</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0300_00_NG.04</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0254_01_1.10</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0228_01_1.01</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0219_00_G.01</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0335_00_G.17</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0228_06_6.05</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0103_01_1.B09</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0103_01_1.B09</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0113_00_G.205</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0228_11_11.01</t>
+          <t>0228_09_9.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0228_11_11.01</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0335_01_1.4</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0001_02_2.347</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0254_01_1.03</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0214_00_G.22</t>
+          <t>0227_02_2.03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0228_09_9.01</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0113_01M_01M.19</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0254_01_1.04</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0335_03_3.4</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0228_06_6.05</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0001_02_2.351</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0219_00_G.01</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0254_01_1.04</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2765,7 +2765,7 @@
         <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0001_02_2.345</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3070,7 +3070,7 @@
         <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0001_02_2.345</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0008_00_G.252</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0113_00_G.200</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0008_02_2.365</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3863,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0001_01_1.270</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0008_02_2.365</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0001_01_1.270</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0008_00_G.252</t>
+          <t>0113_00_G.200</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0001_02_2.347</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0335_02_2.18</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0335_01_1.4</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0300_00_NG.04</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0228_11_11.01</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0335_02_2.4</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0335_02_2.4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5266,7 +5266,7 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5310,12 +5310,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0228_-1_LG.07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5449,7 +5449,7 @@
         <v>30</v>
       </c>
       <c r="F83" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5632,7 +5632,7 @@
         <v>30</v>
       </c>
       <c r="F86" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0113_00_G.200</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5868,7 +5868,7 @@
         <v>30</v>
       </c>
       <c r="F90" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5910,12 +5910,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0113_00_G.205</t>
+          <t>0113_01M_01M.19</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0311_04_4.09</t>
+          <t>0335_02_2.4</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6596,7 +6596,7 @@
         <v>30</v>
       </c>
       <c r="F102" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0113_00_G.200</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0311_04_4.09</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6823,12 +6823,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0335_03_3.4</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0335_02_2.18</t>
+          <t>0113_00_G.200</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0335_02_2.4</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">

--- a/multiSchoolOutput/02_Centre_for_Open_Learning/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/02_Centre_for_Open_Learning/solution_weeks_9_10.xlsx
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0113_00_G.205</t>
+          <t>0228_01_1.01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0201_07_7.02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0254_01_1.04</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0311_04_4.08</t>
+          <t>0335_00_G.17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0254_01_1.03</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0311_04_4.09</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0335_00_G.17</t>
+          <t>0008_-1_B.152</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0228_09_9.01</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0254_01_1.04</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0254_01_1.08</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0228_09_9.01</t>
+          <t>0311_04_4.09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0335_00_G.17</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0311_04_4.09</t>
+          <t>0228_09_9.01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0001_02_2.345</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0228_11_11.01</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0227_02_2.03</t>
+          <t>0214_01_1.10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0254_01_1.03</t>
+          <t>0254_01_1.04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0300_00_NG.04</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0201_07_7.02</t>
+          <t>0311_04_4.08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0001_02_2.347</t>
+          <t>0228_09_9.01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0001_01_1.270</t>
+          <t>0219_00_G.01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0254_01_1.03</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0103_01_1.B09</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0254_01_1.04</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2765,7 +2765,7 @@
         <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2809,12 +2809,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0008_02_2.365</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0001_02_2.345</t>
+          <t>0103_01_1.B09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0335_00_G.09</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3070,7 +3070,7 @@
         <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0001_01_1.270</t>
+          <t>0008_00_G.252</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0335_01_1.4</t>
+          <t>0113_00_G.200</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0300_00_NG.03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0001_02_2.347</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0228_11_11.01</t>
+          <t>0254_01_1.03</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0008_00_G.252</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0228_11_11.11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3863,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0001_02_2.345</t>
+          <t>0335_03_3.4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0001_02_2.343</t>
+          <t>0228_08_8.16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4046,7 +4046,7 @@
         <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0008_02_2.365</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0113_00_G.200</t>
+          <t>0254_01_1.08</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0008_00_G.252</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0228_11_11.01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0103_01_1.B09</t>
+          <t>0008_02_2.365</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0001_01_1.270</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0335_03_3.4</t>
+          <t>0113_00_G.200</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0335_03_3.4</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0335_02_2.18</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0335_02_2.4</t>
+          <t>0113_00_G.11</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5266,7 +5266,7 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5310,12 +5310,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0335_05_5.2</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5449,7 +5449,7 @@
         <v>30</v>
       </c>
       <c r="F83" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0335_05_5.2</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5632,7 +5632,7 @@
         <v>30</v>
       </c>
       <c r="F86" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0113_00_G.205</t>
+          <t>0228_06_6.05</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0113_00_G.200</t>
+          <t>0219_00_G.01</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0335_01_1.9</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5868,7 +5868,7 @@
         <v>30</v>
       </c>
       <c r="F90" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0113_01M_01M.19</t>
+          <t>0113_00_G.205</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0335_02_2.4</t>
+          <t>0001_01_1.270</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0001_02_2.343</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0335_01_1.4</t>
+          <t>0001_02_2.345</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0335_00_G.10</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6596,7 +6596,7 @@
         <v>30</v>
       </c>
       <c r="F102" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0300_00_NG.04</t>
+          <t>0335_01_1.4</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0335_02_2.18</t>
+          <t>0335_02_2.4</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6823,12 +6823,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0335_02_2.18</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0113_00_G.200</t>
+          <t>0335_02_2.4</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0103_01_1.B09</t>
+          <t>0103_01_1.B15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
